--- a/education_forms/043_questionnaire_for_equity_amp_managing_diversity_at_workplace--education_forms.xlsx
+++ b/education_forms/043_questionnaire_for_equity_amp_managing_diversity_at_workplace--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Form Title</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter a title for the form</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,7 +555,11 @@
           <t>Form Category</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select a category for the form</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -574,7 +582,11 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter a brief description of the form</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,38 +601,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>output_survey</t>
+          <t>output_file_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Output Survey</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Output File Name</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter the name of the output file</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>output_file_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>File Type</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select the file type (e.g., PDF, CSV, etc.)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>output_file_size</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>File Size</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the size of the output file</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select the tool assigned for the form</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>survey_description</t>
+          <t>help_message_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Help Message 1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter a help message for the form</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>output_file_name</t>
+          <t>help_message_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Output File</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Help Message 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter another help message for the form</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,361 +763,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>help_message_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Help Message 3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter additional help message for the form</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>output_file_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>File ID</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>output_file_type</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>File Type</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>output_file_size</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>File Size</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>output_file_format</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>File Format</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>help_message</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>help_message_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>help_message_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>kind_input_message</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Kind Input Message</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>help_message_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>help_message_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>help_message_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>help_message_7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>help_message_8</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Help Message</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +860,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1182,46 +877,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>output_file_format_choices</t>
+          <t>output_file_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>output_file_format_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>assigned_tool_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tool_2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tool 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>assigned_tool_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tool_3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
